--- a/LubanTools/DesignerConfigs/Datas/Island/island_config.xlsx
+++ b/LubanTools/DesignerConfigs/Datas/Island/island_config.xlsx
@@ -1216,7 +1216,7 @@
     <col min="5" max="6" width="14" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="76.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="105.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="108.625" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
